--- a/data/output/final_top20_report.xlsx
+++ b/data/output/final_top20_report.xlsx
@@ -483,9 +483,9 @@
     <col width="40" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
@@ -647,38 +647,38 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1411.4</v>
+        <v>1429.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.32</v>
+        <v>-0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>20150.2</v>
+        <v>20411.4</v>
       </c>
       <c r="J2" t="n">
         <v>30.1</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>81.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>75.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="N2" s="4" t="n">
         <v>62.8</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>88.2</v>
+        <v>82.5</v>
       </c>
       <c r="P2" t="n">
         <v>63.3</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Strong Profitability (97/100). bullish technical trend. Sector: Industrials (L2)</t>
+          <t>Strong Financial Health (90/100). bullish technical trend. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1287.2 - 1369.1</t>
+          <t>1298.4 - 1386.8</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>1101.3</v>
+        <v>1118.9</v>
       </c>
       <c r="U2" t="n">
         <v>1552</v>
       </c>
       <c r="V2" t="n">
-        <v>8.926697000000001</v>
+        <v>9.041867</v>
       </c>
       <c r="X2" t="n">
         <v>8.236000000000001</v>
@@ -715,12 +715,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DATAPATTNS.NS</t>
+          <t>GARUDA.NS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Data Patterns (India) Limited</t>
+          <t>Garuda Construction and Engineering Limited</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -739,61 +739,61 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3172.2</v>
+        <v>159.84</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.33</v>
+        <v>1.49</v>
       </c>
       <c r="I3" t="n">
-        <v>17759.2</v>
+        <v>1487.2</v>
       </c>
       <c r="J3" t="n">
-        <v>54.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>70.2</v>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>66.2</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>82.2</v>
+        <v>80.3</v>
       </c>
       <c r="P3" t="n">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Strong Growth (98/100). bullish technical trend. 12% analyst upside. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Growth (98/100). Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 72.0)</t>
+          <t>Sector-level macro risks</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2950.1 - 3077.0</t>
+          <t>155.0 - 176.3</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>2667.7</v>
+        <v>135.9</v>
       </c>
       <c r="U3" t="n">
-        <v>3554.8</v>
+        <v>191.8</v>
       </c>
       <c r="V3" t="n">
-        <v>72.01362</v>
+        <v>13.923346</v>
       </c>
       <c r="X3" t="n">
-        <v>0.378</v>
+        <v>0.023</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -807,85 +807,85 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GANDHITUBE.NS</t>
+          <t>BSE.NS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gandhi Special Tubes Limited</t>
+          <t>BSE Limited</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Metal Fabrication</t>
+          <t>Financial Data &amp; Stock Exchanges</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>807.65</v>
+        <v>2802</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>-3.21</v>
       </c>
       <c r="I4" t="n">
-        <v>985</v>
+        <v>113797.4</v>
       </c>
       <c r="J4" t="n">
-        <v>76.7</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>60.6</v>
+        <v>62.3</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>65.2</v>
+        <v>63.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="P4" t="n">
-        <v>56.7</v>
+        <v>66.7</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Strong Profitability (97/100). neutral-to-positive technicals. Sector: Industrials (L2)</t>
+          <t>Strong Financial Health (100/100). neutral-to-positive technicals. 11% analyst upside. Sector: Financial Services (L1)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>Expensive valuation (PE: 52.9)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>783.4 - 809.6</t>
+          <t>2717.9 - 2803.9</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>686.5</v>
+        <v>2381.7</v>
       </c>
       <c r="U4" t="n">
-        <v>969.2</v>
+        <v>3114.6</v>
       </c>
       <c r="V4" t="n">
-        <v>13.836732</v>
+        <v>52.887882</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -899,85 +899,85 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BSE.NS</t>
+          <t>GANDHITUBE.NS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BSE Limited</t>
+          <t>Gandhi Special Tubes Limited</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Financial Data &amp; Stock Exchanges</t>
+          <t>Metal Fabrication</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2806.1</v>
+        <v>808.95</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33</v>
+        <v>0.95</v>
       </c>
       <c r="I5" t="n">
-        <v>113963.9</v>
+        <v>986.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>49.8</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>63.4</v>
+        <v>65.2</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>81.2</v>
+        <v>77.5</v>
       </c>
       <c r="P5" t="n">
-        <v>66.7</v>
+        <v>56.7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Strong Growth (100/100). bullish technical trend. 11% analyst upside. Sector: Financial Services (L1)</t>
+          <t>Strong Profitability (92/100). neutral-to-positive technicals. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 53.1)</t>
+          <t>Sector-level macro risks</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2721.9 - 2782.8</t>
+          <t>784.7 - 809.7</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>2385.2</v>
+        <v>687.6</v>
       </c>
       <c r="U5" t="n">
-        <v>3114.6</v>
+        <v>970.7</v>
       </c>
       <c r="V5" t="n">
-        <v>53.08551</v>
+        <v>13.847142</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -991,12 +991,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GARUDA.NS</t>
+          <t>VOLTAMP.NS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Garuda Construction and Engineering Limited</t>
+          <t>Voltamp Transformers Limited</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1015,38 +1015,38 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>155.14</v>
+        <v>8604.5</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.16</v>
+        <v>2.29</v>
       </c>
       <c r="I6" t="n">
-        <v>1443.4</v>
+        <v>8705.299999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>76.90000000000001</v>
+        <v>30</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>66.2</v>
+        <v>73.7</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>70.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>79.8</v>
+        <v>75.2</v>
       </c>
       <c r="P6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Strong Growth (100/100). Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Financial Health (90/100). bullish technical trend. 16% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1056,20 +1056,20 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>150.5 - 179.1</t>
+          <t>8229.5 - 8346.4</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>131.9</v>
+        <v>7313.8</v>
       </c>
       <c r="U6" t="n">
-        <v>186.2</v>
+        <v>9994.4</v>
       </c>
       <c r="V6" t="n">
-        <v>13.537521</v>
+        <v>24.570244</v>
       </c>
       <c r="X6" t="n">
-        <v>0.023</v>
+        <v>0.082</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1083,22 +1083,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HBLENGINE.NS</t>
+          <t>FORCEMOT.NS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HBL Engineering Limited</t>
+          <t>FORCE MOTORS LTD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1107,38 +1107,38 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>662.45</v>
+        <v>21585</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>4.17</v>
       </c>
       <c r="I7" t="n">
-        <v>18362.8</v>
+        <v>28441</v>
       </c>
       <c r="J7" t="n">
-        <v>8.1</v>
+        <v>63.3</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>41.1</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>62.3</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>66.8</v>
+        <v>68.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="P7" t="n">
-        <v>50</v>
+        <v>56.7</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Strong Profitability (97/100). Sector: Industrials (L2)</t>
+          <t>Strong Financial Health (100/100). neutral-to-positive technicals. Sector: Consumer Cyclical (L2)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,20 +1148,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>642.6 - 744.4</t>
+          <t>20937.5 - 21533.6</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>563.1</v>
+        <v>18081.4</v>
       </c>
       <c r="U7" t="n">
-        <v>794.9</v>
+        <v>25902</v>
       </c>
       <c r="V7" t="n">
-        <v>23.073843</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.396</v>
+        <v>20.789991</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1175,82 +1172,85 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TATAINVEST.NS</t>
+          <t>QPOWER.NS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tata Investment Corporation Limited</t>
+          <t>Quality Power Electrical Equipments Limited</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>628.8</v>
+        <v>834.55</v>
       </c>
       <c r="H8" t="n">
-        <v>1.14</v>
+        <v>4.76</v>
       </c>
       <c r="I8" t="n">
-        <v>31814.3</v>
+        <v>6463.1</v>
       </c>
       <c r="J8" t="n">
-        <v>73.8</v>
+        <v>75.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>53</v>
+        <v>73.3</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>75.59999999999999</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>64.5</v>
+        <v>63.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>78.8</v>
+        <v>77.7</v>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>56.7</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Strong Profitability (97/100). Sector: Financial Services (L1)</t>
+          <t>Strong Growth (92/100). bullish technical trend. 86% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 77.8)</t>
+          <t>Expensive valuation (PE: 60.6)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>609.9 - 657.3</t>
+          <t>798.9 - 809.5</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>534.5</v>
+        <v>709.4</v>
       </c>
       <c r="U8" t="n">
-        <v>754.6</v>
+        <v>1550</v>
       </c>
       <c r="V8" t="n">
-        <v>77.82178500000001</v>
+        <v>60.606388</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.486</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1264,85 +1264,85 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MCX.NS</t>
+          <t>ACUTAAS.NS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>Acutaas Chemicals Limited</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Financial Data &amp; Stock Exchanges</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2486.1</v>
+        <v>2399.8</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.51</v>
+        <v>7.07</v>
       </c>
       <c r="I9" t="n">
-        <v>63274.8</v>
+        <v>19647.4</v>
       </c>
       <c r="J9" t="n">
-        <v>15.1</v>
+        <v>37.6</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>74</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>67.5</v>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>83.2</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>58.4</v>
+        <v>62.2</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>80.7</v>
+        <v>77.8</v>
       </c>
       <c r="P9" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Strong Growth (100/100). neutral-to-positive technicals. 15% analyst upside. Sector: Financial Services (L1)</t>
+          <t>Strong Growth (98/100). bullish technical trend. Sector: Basic Materials (L3)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 99.5)</t>
+          <t>L3 cyclical stock — earnings volatile across cycles. Expensive valuation (PE: 68.5)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2384.7 - 2411.5</t>
+          <t>2083.8 - 2327.8</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>1949.9</v>
+        <v>1674.1</v>
       </c>
       <c r="U9" t="n">
-        <v>2851.1</v>
+        <v>2131</v>
       </c>
       <c r="V9" t="n">
-        <v>99.483795</v>
+        <v>68.48744000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>0.024</v>
+        <v>0.58</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1380,58 +1380,58 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2863.9</v>
+        <v>2804</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.55</v>
+        <v>-0.57</v>
       </c>
       <c r="I10" t="n">
-        <v>141550.7</v>
+        <v>138590.1</v>
       </c>
       <c r="J10" t="n">
         <v>34.6</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>77.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>73</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>73.8</v>
+        <v>72.8</v>
       </c>
       <c r="P10" t="n">
         <v>66.7</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Strong Growth (100/100). 18% analyst upside. Sector: Financial Services (L1)</t>
+          <t>Strong Profitability (98/100). 21% analyst upside. Sector: Financial Services (L1)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 43.8)</t>
+          <t>Expensive valuation (PE: 42.9)</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2778.0 - 2922.9</t>
+          <t>2719.9 - 2919.7</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>2434.3</v>
+        <v>2383.4</v>
       </c>
       <c r="U10" t="n">
         <v>3392.2</v>
       </c>
       <c r="V10" t="n">
-        <v>43.81061</v>
+        <v>42.920555</v>
       </c>
       <c r="X10" t="n">
         <v>4.117</v>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VOLTAMP.NS</t>
+          <t>BEL.NS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Voltamp Transformers Limited</t>
+          <t>Bharat Electronics Limited</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1472,61 +1472,61 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8372</v>
+        <v>426.1</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.56</v>
+        <v>-1.09</v>
       </c>
       <c r="I11" t="n">
-        <v>8470.1</v>
+        <v>311469.7</v>
       </c>
       <c r="J11" t="n">
-        <v>30</v>
+        <v>53.2</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>73.5</v>
+        <v>72.2</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>68.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>65.8</v>
+        <v>50.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>70.2</v>
+        <v>71.8</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>74.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>70</v>
+        <v>63.3</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). bullish technical trend. 19% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Financial Health (90/100). neutral-to-positive technicals. 14% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>Expensive valuation (PE: 52.1)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>8120.8 - 8189.5</t>
+          <t>413.3 - 434.1</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>7116.2</v>
+        <v>362.2</v>
       </c>
       <c r="U11" t="n">
-        <v>9994.4</v>
+        <v>485.6</v>
       </c>
       <c r="V11" t="n">
-        <v>23.892012</v>
+        <v>52.09046</v>
       </c>
       <c r="X11" t="n">
-        <v>0.082</v>
+        <v>0.273</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1540,85 +1540,85 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ENGINERSIN.NS</t>
+          <t>MCX.NS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Engineers India Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Financial Data &amp; Stock Exchanges</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>187.67</v>
+        <v>2414.5</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.71</v>
+        <v>-4.58</v>
       </c>
       <c r="I12" t="n">
-        <v>10556.2</v>
+        <v>61452.4</v>
       </c>
       <c r="J12" t="n">
-        <v>51.4</v>
+        <v>15.1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>43.8</v>
+        <v>78.09999999999999</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>55.9</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>66.8</v>
+        <v>59</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>75.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>63.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). 32% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Growth (100/100). neutral-to-positive technicals. 19% analyst upside. Sector: Financial Services (L1)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>Expensive valuation (PE: 97.1)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>182.0 - 197.2</t>
+          <t>2342.1 - 2411.0</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>159.5</v>
+        <v>1981.1</v>
       </c>
       <c r="U12" t="n">
-        <v>247</v>
+        <v>2871.1</v>
       </c>
       <c r="V12" t="n">
-        <v>13.599275</v>
+        <v>97.08484</v>
       </c>
       <c r="X12" t="n">
-        <v>0.731</v>
+        <v>0.024</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1632,85 +1632,85 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NATCOPHARM.NS</t>
+          <t>TDPOWERSYS.NS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Natco Pharma Limited</t>
+          <t>TD Power Systems Limited</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>958.55</v>
+        <v>863.25</v>
       </c>
       <c r="H13" t="n">
-        <v>0.28</v>
+        <v>3.57</v>
       </c>
       <c r="I13" t="n">
-        <v>17178.1</v>
+        <v>13485.2</v>
       </c>
       <c r="J13" t="n">
-        <v>51.1</v>
+        <v>28.1</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>74</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>58.4</v>
+        <v>71.09999999999999</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>70.59999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>50</v>
+        <v>73.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). bullish technical trend. Sector: Healthcare (L1)</t>
+          <t>Strong Growth (90/100). bullish technical trend. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>Expensive valuation (PE: 61.4)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>916.9 - 929.8</t>
+          <t>803.5 - 837.4</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>814.8</v>
+        <v>669.4</v>
       </c>
       <c r="U13" t="n">
-        <v>976.6</v>
+        <v>900.5</v>
       </c>
       <c r="V13" t="n">
-        <v>11.020349</v>
+        <v>61.353947</v>
       </c>
       <c r="X13" t="n">
-        <v>3.012</v>
+        <v>3.717</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GVT&amp;D.NS</t>
+          <t>BLS.NS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India Limited</t>
+          <t>BLS International Services Limited</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Specialty Business Services</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1748,61 +1748,61 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3507.2</v>
+        <v>240.6</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.69</v>
+        <v>0.06</v>
       </c>
       <c r="I14" t="n">
-        <v>89800.60000000001</v>
+        <v>9905.299999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>51.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>70.2</v>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>64.2</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>72.2</v>
+        <v>73.7</v>
       </c>
       <c r="P14" t="n">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). neutral-to-positive technicals. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Growth (98/100). 62% analyst upside. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 83.9)</t>
+          <t>Sector-level macro risks</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>3402.0 - 3511.0</t>
+          <t>233.4 - 272.4</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>2886.7</v>
+        <v>204.5</v>
       </c>
       <c r="U14" t="n">
-        <v>3828.6</v>
+        <v>389</v>
       </c>
       <c r="V14" t="n">
-        <v>83.88423</v>
+        <v>15.4131975</v>
       </c>
       <c r="X14" t="n">
-        <v>1.46</v>
+        <v>16.545</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1816,85 +1816,85 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ZENTEC.NS</t>
+          <t>NATCOPHARM.NS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Zen Technologies Limited</t>
+          <t>Natco Pharma Limited</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1340.6</v>
+        <v>959.2</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.77</v>
+        <v>2.25</v>
       </c>
       <c r="I15" t="n">
-        <v>12060.6</v>
+        <v>17184.4</v>
       </c>
       <c r="J15" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="P15" t="n">
         <v>50</v>
       </c>
-      <c r="K15" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="P15" t="n">
-        <v>73.3</v>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Strong Profitability (97/100). 23% analyst upside. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Financial Health (90/100). bullish technical trend. Sector: Healthcare (L1)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 45.7)</t>
+          <t>Sector-level macro risks</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1300.4 - 1362.3</t>
+          <t>921.2 - 930.4</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>1139.5</v>
+        <v>815.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1654</v>
+        <v>987.4</v>
       </c>
       <c r="V15" t="n">
-        <v>45.691887</v>
+        <v>11.037974</v>
       </c>
       <c r="X15" t="n">
-        <v>0.976</v>
+        <v>3.012</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHNOE.NS</t>
+          <t>PIXTRANS.NS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Limited</t>
+          <t>Pix Transmissions Limited</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1932,38 +1932,38 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1075.5</v>
+        <v>1453</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.02</v>
+        <v>1.67</v>
       </c>
       <c r="I16" t="n">
-        <v>12508</v>
+        <v>1983.2</v>
       </c>
       <c r="J16" t="n">
-        <v>57</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>71.3</v>
+        <v>70.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>71.8</v>
+        <v>59.8</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>60.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>71</v>
+        <v>74.7</v>
       </c>
       <c r="P16" t="n">
-        <v>63.3</v>
+        <v>80</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). 53% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Financial Health (90/100). neutral-to-positive technicals. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1973,20 +1973,20 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1043.2 - 1095.8</t>
+          <t>1409.4 - 1430.8</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>914.2</v>
+        <v>1235</v>
       </c>
       <c r="U16" t="n">
-        <v>1650</v>
+        <v>1743.6</v>
       </c>
       <c r="V16" t="n">
-        <v>26.608116</v>
+        <v>18.114948</v>
       </c>
       <c r="X16" t="n">
-        <v>1.573</v>
+        <v>4.661</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EIMCOELECO.NS</t>
+          <t>NAVA.NS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eimco Elecon (India) Limited</t>
+          <t>NAVA LIMITED</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Farm &amp; Heavy Construction Machinery</t>
+          <t>Conglomerates</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2024,38 +2024,38 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1472.7</v>
+        <v>553.5</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.87</v>
+        <v>1.64</v>
       </c>
       <c r="I17" t="n">
-        <v>849.5</v>
+        <v>15664.1</v>
       </c>
       <c r="J17" t="n">
-        <v>53.6</v>
+        <v>54.4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>38.8</v>
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>54.7</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>59.2</v>
+        <v>64.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>76.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="P17" t="n">
         <v>63.3</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Strong Growth (100/100). 34% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Profitability (82/100). Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2065,20 +2065,20 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1428.5 - 1608.0</t>
+          <t>536.9 - 563.9</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1251.8</v>
+        <v>470.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1968</v>
+        <v>664.2</v>
       </c>
       <c r="V17" t="n">
-        <v>17.972906</v>
+        <v>17.604961</v>
       </c>
       <c r="X17" t="n">
-        <v>0.376</v>
+        <v>15.987</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BLS.NS</t>
+          <t>RAJOOENG.NS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BLS International Services Limited</t>
+          <t>Rajoo Engineers Limited</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Specialty Business Services</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2116,38 +2116,38 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>243.4</v>
+        <v>55.89</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.44</v>
+        <v>-0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>10020.6</v>
+        <v>998.6</v>
       </c>
       <c r="J18" t="n">
-        <v>73.09999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>40.4</v>
+        <v>37</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>64.2</v>
+        <v>63.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>74</v>
+        <v>73.2</v>
       </c>
       <c r="P18" t="n">
         <v>80</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Strong Growth (98/100). 60% analyst upside. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Financial Health (90/100). Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2157,20 +2157,20 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>236.1 - 277.7</t>
+          <t>54.2 - 63.1</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>206.9</v>
+        <v>47.5</v>
       </c>
       <c r="U18" t="n">
-        <v>389</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>15.572617</v>
+        <v>15.832861</v>
       </c>
       <c r="X18" t="n">
-        <v>16.545</v>
+        <v>5.21</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2184,85 +2184,82 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SOLARINDS.NS</t>
+          <t>HDFCAMC.NS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Solar Industries India Limited</t>
+          <t>HDFC Asset Management Company Limited</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>14250</v>
+        <v>2390</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.01</v>
+        <v>-0.46</v>
       </c>
       <c r="I19" t="n">
-        <v>128948.3</v>
+        <v>102378</v>
       </c>
       <c r="J19" t="n">
-        <v>43.9</v>
+        <v>56.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>70.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>41.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>71</v>
+        <v>71.8</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>69.59999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Strong Growth (95/100). bullish technical trend. 17% analyst upside. Sector: Basic Materials (L3)</t>
+          <t>Strong Financial Health (100/100). 28% analyst upside. Sector: Financial Services (L1)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>L3 cyclical stock — earnings volatile across cycles. Expensive valuation (PE: 88.5)</t>
+          <t>Sector-level macro risks</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>13652.5 - 13822.5</t>
+          <t>2318.3 - 2585.8</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>12112.5</v>
+        <v>2031.5</v>
       </c>
       <c r="U19" t="n">
-        <v>16696.7</v>
+        <v>3057.5</v>
       </c>
       <c r="V19" t="n">
-        <v>88.487335</v>
-      </c>
-      <c r="X19" t="n">
-        <v>16.425</v>
+        <v>35.676968</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2276,12 +2273,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RAJOOENG.NS</t>
+          <t>TECHNOE.NS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rajoo Engineers Limited</t>
+          <t>Techno Electric &amp; Engineering Company Limited</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2291,7 +2288,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2300,38 +2297,38 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>56.99</v>
+        <v>1089.6</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.49</v>
+        <v>-0.53</v>
       </c>
       <c r="I20" t="n">
-        <v>1018.3</v>
+        <v>12672</v>
       </c>
       <c r="J20" t="n">
-        <v>60.8</v>
+        <v>57</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>38.9</v>
+        <v>70.2</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>51.3</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>63.8</v>
+        <v>69.2</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>80</v>
+        <v>63.3</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Financial Health (90/100). neutral-to-positive technicals. 51% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2341,20 +2338,20 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>55.3 - 64.2</t>
+          <t>1056.9 - 1096.2</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>48.4</v>
+        <v>926.2</v>
       </c>
       <c r="U20" t="n">
-        <v>68.40000000000001</v>
+        <v>1650</v>
       </c>
       <c r="V20" t="n">
-        <v>16.144476</v>
+        <v>26.956953</v>
       </c>
       <c r="X20" t="n">
-        <v>5.21</v>
+        <v>1.573</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2368,85 +2365,88 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>QPOWER.NS</t>
+          <t>SANOFICONR.NS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Quality Power Electrical Equipments Limited</t>
+          <t>Sanofi Consumer Healthcare India Limited</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Drug Manufacturers - General</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>788.85</v>
+        <v>4252</v>
       </c>
       <c r="H21" t="n">
-        <v>1.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>6109.2</v>
+        <v>9806.6</v>
       </c>
       <c r="J21" t="n">
-        <v>75.5</v>
+        <v>71.5</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>51.5</v>
+        <v>56</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>63.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="P21" t="n">
-        <v>56.7</v>
+        <v>57.5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Strong Growth (98/100). neutral-to-positive technicals. 96% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Profitability (98/100). neutral-to-positive technicals. 38% analyst upside. Sector: Healthcare (L1)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 57.3)</t>
+          <t>Expensive valuation (PE: 40.8)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>765.2 - 795.6</t>
+          <t>4124.4 - 4309.4</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>670.5</v>
+        <v>3614.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1550</v>
+        <v>5855</v>
       </c>
       <c r="V21" t="n">
-        <v>57.329212</v>
+        <v>40.817894</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.7309</v>
       </c>
       <c r="X21" t="n">
-        <v>5.486</v>
+        <v>6.458</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>

--- a/data/output/final_top20_report.xlsx
+++ b/data/output/final_top20_report.xlsx
@@ -469,7 +469,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -484,8 +484,8 @@
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
   </cols>
@@ -647,38 +647,38 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1429.7</v>
+        <v>1396.1</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8</v>
+        <v>-2.35</v>
       </c>
       <c r="I2" t="n">
-        <v>20411.4</v>
+        <v>19931.7</v>
       </c>
       <c r="J2" t="n">
         <v>30.1</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L2" s="3" t="n">
         <v>75.90000000000001</v>
       </c>
-      <c r="M2" s="3" t="n">
-        <v>71.59999999999999</v>
+      <c r="M2" s="4" t="n">
+        <v>67</v>
       </c>
       <c r="N2" s="4" t="n">
         <v>62.8</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>82.5</v>
+        <v>81.5</v>
       </c>
       <c r="P2" t="n">
         <v>63.3</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). bullish technical trend. Sector: Industrials (L2)</t>
+          <t>Strong Financial Health (90/100). bullish technical trend. 11% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1298.4 - 1386.8</t>
+          <t>1301.5 - 1354.2</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>1118.9</v>
+        <v>1120.9</v>
       </c>
       <c r="U2" t="n">
         <v>1552</v>
       </c>
       <c r="V2" t="n">
-        <v>9.041867</v>
+        <v>8.8293705</v>
       </c>
       <c r="X2" t="n">
         <v>8.236000000000001</v>
@@ -739,31 +739,31 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>159.84</v>
+        <v>152.98</v>
       </c>
       <c r="H3" t="n">
-        <v>1.49</v>
+        <v>-4.29</v>
       </c>
       <c r="I3" t="n">
-        <v>1487.2</v>
+        <v>1423.4</v>
       </c>
       <c r="J3" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>76.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>43.5</v>
+        <v>34.3</v>
       </c>
       <c r="N3" s="4" t="n">
         <v>66.2</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>80.3</v>
+        <v>78.3</v>
       </c>
       <c r="P3" t="n">
         <v>80</v>
@@ -780,17 +780,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>155.0 - 176.3</t>
+          <t>148.4 - 175.4</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>135.9</v>
+        <v>130</v>
       </c>
       <c r="U3" t="n">
-        <v>191.8</v>
+        <v>183.6</v>
       </c>
       <c r="V3" t="n">
-        <v>13.923346</v>
+        <v>13.325784</v>
       </c>
       <c r="X3" t="n">
         <v>0.023</v>
@@ -831,58 +831,58 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2802</v>
+        <v>2765.4</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.21</v>
+        <v>-1.45</v>
       </c>
       <c r="I4" t="n">
-        <v>113797.4</v>
+        <v>112310.9</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>74.8</v>
+        <v>74.5</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>62.3</v>
+        <v>59.6</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>63.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>79.7</v>
+        <v>79.2</v>
       </c>
       <c r="P4" t="n">
         <v>66.7</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Strong Financial Health (100/100). neutral-to-positive technicals. 11% analyst upside. Sector: Financial Services (L1)</t>
+          <t>Strong Financial Health (100/100). neutral-to-positive technicals. 13% analyst upside. Sector: Financial Services (L1)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 52.9)</t>
+          <t>Expensive valuation (PE: 52.1)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2717.9 - 2803.9</t>
+          <t>2682.4 - 2801.5</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>2381.7</v>
+        <v>2350.6</v>
       </c>
       <c r="U4" t="n">
         <v>3114.6</v>
       </c>
       <c r="V4" t="n">
-        <v>52.887882</v>
+        <v>52.13801</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -899,12 +899,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GANDHITUBE.NS</t>
+          <t>DATAPATTNS.NS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gandhi Special Tubes Limited</t>
+          <t>Data Patterns (India) Limited</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metal Fabrication</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -923,61 +923,61 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>808.95</v>
+        <v>3161.7</v>
       </c>
       <c r="H5" t="n">
-        <v>0.95</v>
+        <v>-2.14</v>
       </c>
       <c r="I5" t="n">
-        <v>986.6</v>
+        <v>17700.5</v>
       </c>
       <c r="J5" t="n">
-        <v>76.7</v>
+        <v>54.7</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>73.8</v>
+        <v>74</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>49.8</v>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>61.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>65.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>77.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>56.7</v>
+        <v>73.3</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Strong Profitability (92/100). neutral-to-positive technicals. Sector: Industrials (L2)</t>
+          <t>Strong Growth (90/100). bullish technical trend. 12% analyst upside. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>Expensive valuation (PE: 71.4)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>784.7 - 809.7</t>
+          <t>3061.4 - 3066.8</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>687.6</v>
+        <v>2687.4</v>
       </c>
       <c r="U5" t="n">
-        <v>970.7</v>
+        <v>3554.8</v>
       </c>
       <c r="V5" t="n">
-        <v>13.847142</v>
+        <v>71.43471</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04</v>
+        <v>0.378</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -991,12 +991,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VOLTAMP.NS</t>
+          <t>GANDHITUBE.NS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Voltamp Transformers Limited</t>
+          <t>Gandhi Special Tubes Limited</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Metal Fabrication</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1015,38 +1015,38 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8604.5</v>
+        <v>806.55</v>
       </c>
       <c r="H6" t="n">
-        <v>2.29</v>
+        <v>0.42</v>
       </c>
       <c r="I6" t="n">
-        <v>8705.299999999999</v>
+        <v>983.7</v>
       </c>
       <c r="J6" t="n">
-        <v>30</v>
+        <v>76.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>70.2</v>
+        <v>73.8</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>65.2</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>75.2</v>
+        <v>77.5</v>
       </c>
       <c r="P6" t="n">
-        <v>70</v>
+        <v>56.7</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). bullish technical trend. 16% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Profitability (92/100). neutral-to-positive technicals. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1056,20 +1056,20 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>8229.5 - 8346.4</t>
+          <t>782.4 - 809.3</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>7313.8</v>
+        <v>685.6</v>
       </c>
       <c r="U6" t="n">
-        <v>9994.4</v>
+        <v>967.9</v>
       </c>
       <c r="V6" t="n">
-        <v>24.570244</v>
+        <v>13.813153</v>
       </c>
       <c r="X6" t="n">
-        <v>0.082</v>
+        <v>0.04</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1083,22 +1083,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FORCEMOT.NS</t>
+          <t>ENGINERSIN.NS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FORCE MOTORS LTD</t>
+          <t>Engineers India Limited</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1107,38 +1107,38 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>21585</v>
+        <v>186.05</v>
       </c>
       <c r="H7" t="n">
-        <v>4.17</v>
+        <v>-2.92</v>
       </c>
       <c r="I7" t="n">
-        <v>28441</v>
+        <v>10465.1</v>
       </c>
       <c r="J7" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="P7" t="n">
         <v>63.3</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="P7" t="n">
-        <v>56.7</v>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Strong Financial Health (100/100). neutral-to-positive technicals. Sector: Consumer Cyclical (L2)</t>
+          <t>Strong Financial Health (90/100). 33% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1148,17 +1148,20 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>20937.5 - 21533.6</t>
+          <t>180.5 - 195.7</t>
         </is>
       </c>
       <c r="T7" t="n">
-        <v>18081.4</v>
+        <v>158.1</v>
       </c>
       <c r="U7" t="n">
-        <v>25902</v>
+        <v>247</v>
       </c>
       <c r="V7" t="n">
-        <v>20.789991</v>
+        <v>13.481884</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.731</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1172,85 +1175,85 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>QPOWER.NS</t>
+          <t>ICICIAMC.NS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quality Power Electrical Equipments Limited</t>
+          <t>ICICI Prudential Asset Management Company Limited</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>834.55</v>
+        <v>2718</v>
       </c>
       <c r="H8" t="n">
-        <v>4.76</v>
+        <v>-3.07</v>
       </c>
       <c r="I8" t="n">
-        <v>6463.1</v>
+        <v>134339.5</v>
       </c>
       <c r="J8" t="n">
-        <v>75.5</v>
+        <v>34.6</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>63.2</v>
+        <v>72</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>73</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>77.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>56.7</v>
+        <v>66.7</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Strong Growth (92/100). bullish technical trend. 86% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Profitability (98/100). 25% analyst upside. Sector: Financial Services (L1)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 60.6)</t>
+          <t>Expensive valuation (PE: 41.6)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>798.9 - 809.5</t>
+          <t>2636.5 - 2911.3</t>
         </is>
       </c>
       <c r="T8" t="n">
-        <v>709.4</v>
+        <v>2310.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1550</v>
+        <v>3392.2</v>
       </c>
       <c r="V8" t="n">
-        <v>60.606388</v>
+        <v>41.604164</v>
       </c>
       <c r="X8" t="n">
-        <v>5.486</v>
+        <v>4.117</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1264,85 +1267,85 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ACUTAAS.NS</t>
+          <t>VOLTAMP.NS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals Limited</t>
+          <t>Voltamp Transformers Limited</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Specialty Chemicals</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2399.8</v>
+        <v>8309</v>
       </c>
       <c r="H9" t="n">
-        <v>7.07</v>
+        <v>-3.43</v>
       </c>
       <c r="I9" t="n">
-        <v>19647.4</v>
+        <v>8406.299999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>37.6</v>
+        <v>30</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="N9" s="4" t="n">
-        <v>62.2</v>
+        <v>71.7</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>70.2</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>77.8</v>
+        <v>72.3</v>
       </c>
       <c r="P9" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Strong Growth (98/100). bullish technical trend. Sector: Basic Materials (L3)</t>
+          <t>Strong Financial Health (90/100). neutral-to-positive technicals. 20% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>L3 cyclical stock — earnings volatile across cycles. Expensive valuation (PE: 68.5)</t>
+          <t>Sector-level macro risks</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2083.8 - 2327.8</t>
+          <t>8059.7 - 8289.0</t>
         </is>
       </c>
       <c r="T9" t="n">
-        <v>1674.1</v>
+        <v>7062.6</v>
       </c>
       <c r="U9" t="n">
-        <v>2131</v>
+        <v>9994.4</v>
       </c>
       <c r="V9" t="n">
-        <v>68.48744000000001</v>
+        <v>23.72644</v>
       </c>
       <c r="X9" t="n">
-        <v>0.58</v>
+        <v>0.082</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1356,85 +1359,85 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ICICIAMC.NS</t>
+          <t>CPPLUS.NS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Limited</t>
+          <t>Aditya Infotech Limited</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Building Products &amp; Equipment</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2804</v>
+        <v>1697.3</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.57</v>
+        <v>-1.28</v>
       </c>
       <c r="I10" t="n">
-        <v>138590.1</v>
+        <v>19993.9</v>
       </c>
       <c r="J10" t="n">
-        <v>34.6</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>73</v>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>66.40000000000001</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>72.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>66.7</v>
+        <v>56.7</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Strong Profitability (98/100). 21% analyst upside. Sector: Financial Services (L1)</t>
+          <t>Strong Growth (98/100). bullish technical trend. 15% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 42.9)</t>
+          <t>Expensive valuation (PE: 78.4)</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2719.9 - 2919.7</t>
+          <t>1573.9 - 1646.4</t>
         </is>
       </c>
       <c r="T10" t="n">
-        <v>2383.4</v>
+        <v>1442.7</v>
       </c>
       <c r="U10" t="n">
-        <v>3392.2</v>
+        <v>1954</v>
       </c>
       <c r="V10" t="n">
-        <v>42.920555</v>
+        <v>78.36104</v>
       </c>
       <c r="X10" t="n">
-        <v>4.117</v>
+        <v>8.041</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1448,12 +1451,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BEL.NS</t>
+          <t>GVT&amp;D.NS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bharat Electronics Limited</t>
+          <t>GE Vernova T&amp;D India Limited</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1463,7 +1466,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1472,61 +1475,61 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>426.1</v>
+        <v>3486.3</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.09</v>
+        <v>-5.24</v>
       </c>
       <c r="I11" t="n">
-        <v>311469.7</v>
+        <v>89265.5</v>
       </c>
       <c r="J11" t="n">
-        <v>53.2</v>
+        <v>51.7</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>71.8</v>
+        <v>71.59999999999999</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="P11" t="n">
-        <v>63.3</v>
+        <v>73.3</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). neutral-to-positive technicals. 14% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Financial Health (90/100). neutral-to-positive technicals. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 52.1)</t>
+          <t>Expensive valuation (PE: 83.9)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>413.3 - 434.1</t>
+          <t>3381.7 - 3498.7</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>362.2</v>
+        <v>2939.4</v>
       </c>
       <c r="U11" t="n">
-        <v>485.6</v>
+        <v>3828.6</v>
       </c>
       <c r="V11" t="n">
-        <v>52.09046</v>
+        <v>83.86577</v>
       </c>
       <c r="X11" t="n">
-        <v>0.273</v>
+        <v>1.46</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1540,85 +1543,85 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MCX.NS</t>
+          <t>HBLENGINE.NS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Limited</t>
+          <t>HBL Engineering Limited</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Financial Data &amp; Stock Exchanges</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2414.5</v>
+        <v>643.75</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.58</v>
+        <v>-2.39</v>
       </c>
       <c r="I12" t="n">
-        <v>61452.4</v>
+        <v>17844.4</v>
       </c>
       <c r="J12" t="n">
-        <v>15.1</v>
+        <v>8.1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>55.9</v>
+        <v>74.09999999999999</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>37.9</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>59</v>
+        <v>66.8</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Strong Growth (100/100). neutral-to-positive technicals. 19% analyst upside. Sector: Financial Services (L1)</t>
+          <t>Strong Profitability (92/100). Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 97.1)</t>
+          <t>Sector-level macro risks</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2342.1 - 2411.0</t>
+          <t>624.4 - 728.8</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>1981.1</v>
+        <v>547.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2871.1</v>
+        <v>772.5</v>
       </c>
       <c r="V12" t="n">
-        <v>97.08484</v>
+        <v>22.438131</v>
       </c>
       <c r="X12" t="n">
-        <v>0.024</v>
+        <v>4.396</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1632,12 +1635,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TDPOWERSYS.NS</t>
+          <t>BEL.NS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TD Power Systems Limited</t>
+          <t>Bharat Electronics Limited</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1647,7 +1650,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1656,61 +1659,61 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>863.25</v>
+        <v>414.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.57</v>
+        <v>-2.75</v>
       </c>
       <c r="I13" t="n">
-        <v>13485.2</v>
+        <v>302917.2</v>
       </c>
       <c r="J13" t="n">
-        <v>28.1</v>
+        <v>53.2</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>69.59999999999999</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>43.2</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="P13" t="n">
-        <v>73.3</v>
+        <v>63.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Strong Growth (90/100). bullish technical trend. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Financial Health (90/100). neutral-to-positive technicals. 17% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 61.4)</t>
+          <t>Expensive valuation (PE: 50.7)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>803.5 - 837.4</t>
+          <t>402.0 - 433.2</t>
         </is>
       </c>
       <c r="T13" t="n">
-        <v>669.4</v>
+        <v>352.2</v>
       </c>
       <c r="U13" t="n">
-        <v>900.5</v>
+        <v>485.6</v>
       </c>
       <c r="V13" t="n">
-        <v>61.353947</v>
+        <v>50.660145</v>
       </c>
       <c r="X13" t="n">
-        <v>3.717</v>
+        <v>0.273</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1724,85 +1727,85 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BLS.NS</t>
+          <t>ACUTAAS.NS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BLS International Services Limited</t>
+          <t>Acutaas Chemicals Limited</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Specialty Business Services</t>
+          <t>Specialty Chemicals</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>240.6</v>
+        <v>2350.7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06</v>
+        <v>-2.05</v>
       </c>
       <c r="I14" t="n">
-        <v>9905.299999999999</v>
+        <v>19245.4</v>
       </c>
       <c r="J14" t="n">
-        <v>73.09999999999999</v>
+        <v>37.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>37.5</v>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>64.2</v>
+        <v>59.7</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>73.7</v>
+        <v>76.2</v>
       </c>
       <c r="P14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Strong Growth (98/100). 62% analyst upside. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Growth (98/100). bullish technical trend. Sector: Basic Materials (L3)</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>L3 cyclical stock — earnings volatile across cycles. Expensive valuation (PE: 67.1)</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>233.4 - 272.4</t>
+          <t>2083.8 - 2280.2</t>
         </is>
       </c>
       <c r="T14" t="n">
-        <v>204.5</v>
+        <v>1680.6</v>
       </c>
       <c r="U14" t="n">
-        <v>389</v>
+        <v>2131</v>
       </c>
       <c r="V14" t="n">
-        <v>15.4131975</v>
+        <v>67.08618</v>
       </c>
       <c r="X14" t="n">
-        <v>16.545</v>
+        <v>0.58</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1816,22 +1819,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NATCOPHARM.NS</t>
+          <t>MCX.NS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Natco Pharma Limited</t>
+          <t>Multi Commodity Exchange of India Limited</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - Specialty &amp; Generic</t>
+          <t>Financial Data &amp; Stock Exchanges</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1840,61 +1843,61 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>959.2</v>
+        <v>2324.7</v>
       </c>
       <c r="H15" t="n">
-        <v>2.25</v>
+        <v>-3.72</v>
       </c>
       <c r="I15" t="n">
-        <v>17184.4</v>
+        <v>59166.9</v>
       </c>
       <c r="J15" t="n">
-        <v>51.1</v>
+        <v>15.1</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>71.8</v>
+        <v>78.09999999999999</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>48.5</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>53.7</v>
+        <v>59</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>77.8</v>
+        <v>75.8</v>
       </c>
       <c r="P15" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). bullish technical trend. Sector: Healthcare (L1)</t>
+          <t>Strong Growth (100/100). neutral-to-positive technicals. 24% analyst upside. Sector: Financial Services (L1)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>Expensive valuation (PE: 93.5)</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>921.2 - 930.4</t>
+          <t>2255.0 - 2407.7</t>
         </is>
       </c>
       <c r="T15" t="n">
-        <v>815.3</v>
+        <v>1976</v>
       </c>
       <c r="U15" t="n">
-        <v>987.4</v>
+        <v>2871.1</v>
       </c>
       <c r="V15" t="n">
-        <v>11.037974</v>
+        <v>93.47405999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>3.012</v>
+        <v>0.024</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1908,22 +1911,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PIXTRANS.NS</t>
+          <t>FORCEMOT.NS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pix Transmissions Limited</t>
+          <t>FORCE MOTORS LTD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Auto Manufacturers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1932,38 +1935,38 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1453</v>
+        <v>20860</v>
       </c>
       <c r="H16" t="n">
-        <v>1.67</v>
+        <v>-3.36</v>
       </c>
       <c r="I16" t="n">
-        <v>1983.2</v>
+        <v>27485.7</v>
       </c>
       <c r="J16" t="n">
-        <v>66.90000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>59.8</v>
+        <v>70.7</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>48.8</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>60.8</v>
+        <v>66.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>74.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>80</v>
+        <v>56.7</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). neutral-to-positive technicals. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Financial Health (100/100). neutral-to-positive technicals. Sector: Consumer Cyclical (L2)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1973,20 +1976,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1409.4 - 1430.8</t>
+          <t>20234.2 - 21503.0</t>
         </is>
       </c>
       <c r="T16" t="n">
-        <v>1235</v>
+        <v>17731</v>
       </c>
       <c r="U16" t="n">
-        <v>1743.6</v>
+        <v>25032</v>
       </c>
       <c r="V16" t="n">
-        <v>18.114948</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.661</v>
+        <v>20.091694</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAVA.NS</t>
+          <t>ATLANTAELE.NS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NAVA LIMITED</t>
+          <t>Atlanta Electricals Limited</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Conglomerates</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2024,61 +2024,61 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>553.5</v>
+        <v>1127.25</v>
       </c>
       <c r="H17" t="n">
-        <v>1.64</v>
+        <v>-4.41</v>
       </c>
       <c r="I17" t="n">
-        <v>15664.1</v>
+        <v>8668.200000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>54.4</v>
+        <v>87.3</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>70.40000000000001</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>54.7</v>
+        <v>64.40000000000001</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>64.8</v>
+        <v>65.2</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>63.3</v>
+        <v>73.3</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Strong Profitability (82/100). Sector: Industrials (L2)</t>
+          <t>Strong Growth (96/100). bullish technical trend. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>Expensive valuation (PE: 66.9)</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>536.9 - 563.9</t>
+          <t>932.3 - 1093.4</t>
         </is>
       </c>
       <c r="T17" t="n">
-        <v>470.5</v>
+        <v>958.2</v>
       </c>
       <c r="U17" t="n">
-        <v>664.2</v>
+        <v>1352.7</v>
       </c>
       <c r="V17" t="n">
-        <v>17.604961</v>
+        <v>66.85943</v>
       </c>
       <c r="X17" t="n">
-        <v>15.987</v>
+        <v>46.263</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RAJOOENG.NS</t>
+          <t>BLS.NS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rajoo Engineers Limited</t>
+          <t>BLS International Services Limited</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Specialty Business Services</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2116,38 +2116,38 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>55.89</v>
+        <v>233.75</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2</v>
+        <v>-2.85</v>
       </c>
       <c r="I18" t="n">
-        <v>998.6</v>
+        <v>9623.299999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>60.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>37</v>
+        <v>34.3</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>63.8</v>
+        <v>64.2</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="P18" t="n">
         <v>80</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). Sector: Industrials (L2). strong Bandhan strategy alignment</t>
+          <t>Strong Growth (98/100). 66% analyst upside. Sector: Industrials (L2). strong Bandhan strategy alignment</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2157,20 +2157,20 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>54.2 - 63.1</t>
+          <t>226.7 - 270.8</t>
         </is>
       </c>
       <c r="T18" t="n">
-        <v>47.5</v>
+        <v>198.7</v>
       </c>
       <c r="U18" t="n">
-        <v>67.09999999999999</v>
+        <v>389</v>
       </c>
       <c r="V18" t="n">
-        <v>15.832861</v>
+        <v>14.974376</v>
       </c>
       <c r="X18" t="n">
-        <v>5.21</v>
+        <v>16.545</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2184,82 +2184,85 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HDFCAMC.NS</t>
+          <t>QPOWER.NS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Limited</t>
+          <t>Quality Power Electrical Equipments Limited</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2390</v>
+        <v>810.8</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.46</v>
+        <v>-2.85</v>
       </c>
       <c r="I19" t="n">
-        <v>102378</v>
+        <v>6279.2</v>
       </c>
       <c r="J19" t="n">
-        <v>56.5</v>
+        <v>75.5</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>70.2</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>69.59999999999999</v>
+      <c r="L19" s="4" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>73.2</v>
       </c>
       <c r="P19" t="n">
-        <v>66.7</v>
+        <v>56.7</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Strong Financial Health (100/100). 28% analyst upside. Sector: Financial Services (L1)</t>
+          <t>Strong Growth (92/100). bullish technical trend. 91% analyst upside. Sector: Industrials (L2)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Sector-level macro risks</t>
+          <t>Expensive valuation (PE: 58.9)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2318.3 - 2585.8</t>
+          <t>786.5 - 799.0</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>2031.5</v>
+        <v>689.2</v>
       </c>
       <c r="U19" t="n">
-        <v>3057.5</v>
+        <v>1550</v>
       </c>
       <c r="V19" t="n">
-        <v>35.676968</v>
+        <v>58.881622</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.486</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2273,62 +2276,62 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TECHNOE.NS</t>
+          <t>HDFCAMC.NS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Limited</t>
+          <t>HDFC Asset Management Company Limited</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1089.6</v>
+        <v>2350</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.53</v>
+        <v>-1.5</v>
       </c>
       <c r="I20" t="n">
-        <v>12672</v>
+        <v>100674</v>
       </c>
       <c r="J20" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>70.09999999999999</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>68.7</v>
       </c>
       <c r="P20" t="n">
-        <v>63.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Strong Financial Health (90/100). neutral-to-positive technicals. 51% analyst upside. Sector: Industrials (L2)</t>
+          <t>Strong Financial Health (100/100). 30% analyst upside. Sector: Financial Services (L1)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2338,20 +2341,17 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1056.9 - 1096.2</t>
+          <t>2279.5 - 2574.9</t>
         </is>
       </c>
       <c r="T20" t="n">
-        <v>926.2</v>
+        <v>1997.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1650</v>
+        <v>3057.5</v>
       </c>
       <c r="V20" t="n">
-        <v>26.956953</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.573</v>
+        <v>35.174377</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2365,12 +2365,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANOFICONR.NS</t>
+          <t>NATCOPHARM.NS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sanofi Consumer Healthcare India Limited</t>
+          <t>Natco Pharma Limited</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Drug Manufacturers - General</t>
+          <t>Drug Manufacturers - Specialty &amp; Generic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2389,64 +2389,61 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4252</v>
+        <v>948.4</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8100000000000001</v>
+        <v>-1.13</v>
       </c>
       <c r="I21" t="n">
-        <v>9806.6</v>
+        <v>16990.9</v>
       </c>
       <c r="J21" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>70.2</v>
+        <v>51.1</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>69.90000000000001</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>56</v>
+        <v>62.2</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>56.2</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>71.5</v>
+        <v>75.8</v>
       </c>
       <c r="P21" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Strong Profitability (98/100). neutral-to-positive technicals. 38% analyst upside. Sector: Healthcare (L1)</t>
+          <t>Strong Financial Health (90/100). bullish technical trend. Sector: Healthcare (L1)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Expensive valuation (PE: 40.8)</t>
+          <t>Sector-level macro risks</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>4124.4 - 4309.4</t>
+          <t>919.9 - 922.0</t>
         </is>
       </c>
       <c r="T21" t="n">
-        <v>3614.2</v>
+        <v>806.1</v>
       </c>
       <c r="U21" t="n">
-        <v>5855</v>
+        <v>987.4</v>
       </c>
       <c r="V21" t="n">
-        <v>40.817894</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.7309</v>
+        <v>10.913694</v>
       </c>
       <c r="X21" t="n">
-        <v>6.458</v>
+        <v>3.012</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
